--- a/222/222_222/002_AES2/条件输入数据表.xlsx
+++ b/222/222_222/002_AES2/条件输入数据表.xlsx
@@ -1836,62 +1836,62 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>绝热材料</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr"/>
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>岩棉毡</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t>岩棉毡</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>绝热材料厚度</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="0" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>绝热材料密度</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>kg/m³</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="0" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1900,9 +1900,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="H1:H2"/>
-    <mergeCell ref="K1:L1"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1980,7 +1980,7 @@
       <c r="C3" s="33" t="inlineStr"/>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>欧标系列</t>
+          <t>/</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,11 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr"/>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="28" t="inlineStr">
@@ -2253,26 +2257,26 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>表面处理标准</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr"/>
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>GB/T 8923-2011</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>表面处理合格级别</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr"/>
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>Sa2.5级</t>
         </is>
